--- a/Intersecciones/excels/JUNIN-HUANCAYO-HUANCAN.xlsx
+++ b/Intersecciones/excels/JUNIN-HUANCAYO-HUANCAN.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-365234</t>
+          <t>I-586081</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,17 +508,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-12.1149032</t>
+          <t>-12.1050045</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-75.2239647</t>
+          <t>-75.1896098</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-586081</t>
+          <t>I-429891</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-12.1050045</t>
+          <t>-12.1167394</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-75.1896098</t>
+          <t>-75.2079317</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-709946</t>
+          <t>I-429902</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -612,25 +612,857 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-12.1145352</t>
+          <t>-12.1036878</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-75.2239932</t>
+          <t>-75.2137502</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>I-429889</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-12.1157315</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-75.2114871</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>I-429904</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-12.1087767</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-75.2109285</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Jirón La Cantuta / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>I-429906</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-12.1066198</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-75.210129</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Jirón 2 de Mayo / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>I-429909</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-12.1064244</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-75.2091917</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Jirón 2 de Mayo / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>I-429917</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-12.1198293</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-75.2002194</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-429919</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-12.1101095</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-75.1984968</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>I-429877</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-12.1062481</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-75.2037093</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>I-429870</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-12.1120846</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-75.2043745</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>I-429872</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-12.1155062</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-75.203602</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>I-429875</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-12.1078765</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-75.2041963</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>I-429928</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-12.1070906</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-75.2024674</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>I-429920</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-12.1111568</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-75.1919089</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>I-429923</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-12.1107386</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-75.1964834</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>I-429924</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-12.1111161</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-75.1947427</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>I-429930</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-12.1119293</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-75.2012882</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Calle Curacas I / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>I-429931</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-12.1110034</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-75.2015018</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>120119</t>
         </is>

--- a/Intersecciones/excels/JUNIN-HUANCAYO-HUANCAN.xlsx
+++ b/Intersecciones/excels/JUNIN-HUANCAYO-HUANCAN.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1468,6 +1468,162 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>I-429866</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-12.1135784</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-75.2038358</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>I-429879</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-12.1061766</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-75.202619</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>I-429880</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-12.1060888</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-75.201868</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/JUNIN-HUANCAYO-HUANCAN.xlsx
+++ b/Intersecciones/excels/JUNIN-HUANCAYO-HUANCAN.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1624,6 +1624,110 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>I-429864</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-12.1213463</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-75.2034236</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>I-429867</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-12.1144893</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-75.2036258</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>120119</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/JUNIN-HUANCAYO-HUANCAN.xlsx
+++ b/Intersecciones/excels/JUNIN-HUANCAYO-HUANCAN.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-586081</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-12.1050045</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-429891</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-12.1167394</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-429902</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-12.1036878</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-429889</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-12.1157315</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-429904</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-12.1087767</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-429906</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-12.1066198</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-429909</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-12.1064244</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-429917</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-12.1198293</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-429919</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-12.1101095</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-429877</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-12.1062481</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-429870</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-12.1120846</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-429872</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-12.1155062</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-429875</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-12.1078765</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-429928</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-12.1070906</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-429920</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-12.1111568</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-429923</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-12.1107386</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-429924</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-12.1111161</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-429930</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-12.1119293</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-429931</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-12.1110034</t>
@@ -1460,40 +1365,35 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>I-429866</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-12.1135784</t>
@@ -1512,40 +1412,35 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>I-429879</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-12.1061766</t>
@@ -1564,40 +1459,35 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>I-429880</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-12.1060888</t>
@@ -1616,40 +1506,35 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>I-429864</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-12.1213463</t>
@@ -1668,40 +1553,35 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>120119</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HUANCAYO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HUANCAN</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>I-429867</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>120119</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>HUANCAN</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-12.1144893</t>
@@ -1720,11 +1600,6 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>120119</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/JUNIN-HUANCAYO-HUANCAN.xlsx
+++ b/Intersecciones/excels/JUNIN-HUANCAYO-HUANCAN.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/JUNIN-HUANCAYO-HUANCAN.xlsx
+++ b/Intersecciones/excels/JUNIN-HUANCAYO-HUANCAN.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/JUNIN-HUANCAYO-HUANCAN.xlsx
+++ b/Intersecciones/excels/JUNIN-HUANCAYO-HUANCAN.xlsx
@@ -533,17 +533,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-429891</t>
+          <t>I-429931</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-12.1167394</t>
+          <t>-12.1110034</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-75.2079317</t>
+          <t>-75.2015018</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -580,22 +580,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-429902</t>
+          <t>I-429930</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-12.1036878</t>
+          <t>-12.1119293</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-75.2137502</t>
+          <t>-75.2012882</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle Curacas I / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -627,17 +627,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-429889</t>
+          <t>I-429928</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-12.1157315</t>
+          <t>-12.1070906</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-75.2114871</t>
+          <t>-75.2024674</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-429904</t>
+          <t>I-429924</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-12.1087767</t>
+          <t>-12.1111161</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-75.2109285</t>
+          <t>-75.1947427</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Jirón La Cantuta / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,22 +721,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-429906</t>
+          <t>I-429923</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-12.1066198</t>
+          <t>-12.1107386</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-75.210129</t>
+          <t>-75.1964834</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Jirón 2 de Mayo / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-429909</t>
+          <t>I-429920</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-12.1064244</t>
+          <t>-12.1111568</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-75.2091917</t>
+          <t>-75.1919089</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jirón 2 de Mayo / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -815,17 +815,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-429917</t>
+          <t>I-429919</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-12.1198293</t>
+          <t>-12.1101095</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-75.2002194</t>
+          <t>-75.1984968</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -862,17 +862,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-429919</t>
+          <t>I-429917</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-12.1101095</t>
+          <t>-12.1198293</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-75.1984968</t>
+          <t>-75.2002194</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -909,22 +909,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-429877</t>
+          <t>I-429909</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-12.1062481</t>
+          <t>-12.1064244</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-75.2037093</t>
+          <t>-75.2091917</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jirón 2 de Mayo / Calle s / n</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-429870</t>
+          <t>I-429906</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-12.1120846</t>
+          <t>-12.1066198</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-75.2043745</t>
+          <t>-75.210129</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jirón 2 de Mayo / Calle s / n</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1003,22 +1003,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-429872</t>
+          <t>I-429904</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-12.1155062</t>
+          <t>-12.1087767</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-75.203602</t>
+          <t>-75.2109285</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jirón La Cantuta / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1050,17 +1050,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-429875</t>
+          <t>I-429902</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-12.1078765</t>
+          <t>-12.1036878</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-75.2041963</t>
+          <t>-75.2137502</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-429928</t>
+          <t>I-429891</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-12.1070906</t>
+          <t>-12.1167394</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-75.2024674</t>
+          <t>-75.2079317</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-429920</t>
+          <t>I-429889</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-12.1111568</t>
+          <t>-12.1157315</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-75.1919089</t>
+          <t>-75.2114871</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-429923</t>
+          <t>I-429880</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-12.1107386</t>
+          <t>-12.1060888</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-75.1964834</t>
+          <t>-75.201868</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1238,17 +1238,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-429924</t>
+          <t>I-429879</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-12.1111161</t>
+          <t>-12.1061766</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-75.1947427</t>
+          <t>-75.202619</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1285,22 +1285,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-429930</t>
+          <t>I-429877</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-12.1119293</t>
+          <t>-12.1062481</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-75.2012882</t>
+          <t>-75.2037093</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Calle Curacas I / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1332,17 +1332,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-429931</t>
+          <t>I-429875</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-12.1110034</t>
+          <t>-12.1078765</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-75.2015018</t>
+          <t>-75.2041963</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1379,17 +1379,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-429866</t>
+          <t>I-429872</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-12.1135784</t>
+          <t>-12.1155062</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-75.2038358</t>
+          <t>-75.203602</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-429879</t>
+          <t>I-429870</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-12.1061766</t>
+          <t>-12.1120846</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-75.202619</t>
+          <t>-75.2043745</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-429880</t>
+          <t>I-429867</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-12.1060888</t>
+          <t>-12.1144893</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-75.201868</t>
+          <t>-75.2036258</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-429864</t>
+          <t>I-429866</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-12.1213463</t>
+          <t>-12.1135784</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-75.2034236</t>
+          <t>-75.2038358</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1567,17 +1567,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-429867</t>
+          <t>I-429864</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-12.1144893</t>
+          <t>-12.1213463</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-75.2036258</t>
+          <t>-75.2034236</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
